--- a/july 2026/GT_JULY_26/29-07-2026/Zesahn ok.xlsx
+++ b/july 2026/GT_JULY_26/29-07-2026/Zesahn ok.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE92C26F-97CB-4B9D-A1F3-5612DA9BA8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65021E7-E199-4684-A693-FA809176B867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -7150,7 +7150,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -7178,7 +7178,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -7968,6 +7968,9 @@
       <c r="P22" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>40</v>
       </c>
       <c r="S22" s="269">
         <v>0.05</v>
@@ -8555,7 +8558,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -8583,7 +8586,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -9966,7 +9969,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -9994,7 +9997,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -11377,7 +11380,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -11405,7 +11408,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -12784,7 +12787,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -12812,7 +12815,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -13383,6 +13386,9 @@
       <c r="P19" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>6</v>
       </c>
       <c r="S19" s="269">
         <f>+S18</f>
@@ -14189,7 +14195,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -14217,7 +14223,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -15596,7 +15602,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -15624,7 +15630,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -16418,6 +16424,9 @@
       <c r="P22" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>12</v>
       </c>
       <c r="S22" s="269">
         <v>0.05</v>
@@ -17005,7 +17014,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -17033,7 +17042,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -17384,7 +17393,9 @@
         <f>M16+N16+O16</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="142"/>
+      <c r="Q16" s="142">
+        <v>6</v>
+      </c>
       <c r="S16" s="269">
         <v>0.08</v>
       </c>
@@ -17458,6 +17469,9 @@
         <f t="shared" ref="P17:P24" si="5">M17+N17+O17</f>
         <v>0</v>
       </c>
+      <c r="Q17">
+        <v>6</v>
+      </c>
       <c r="S17" s="269">
         <f>+S16</f>
         <v>0.08</v>
@@ -17823,6 +17837,9 @@
       <c r="P22" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>12</v>
       </c>
       <c r="S22" s="269">
         <v>0.05</v>
@@ -18410,7 +18427,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -18438,7 +18455,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -19228,6 +19245,9 @@
       <c r="P22" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>80</v>
       </c>
       <c r="S22" s="269">
         <v>0.05</v>
@@ -19815,7 +19835,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -19843,7 +19863,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -23638,7 +23658,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -23666,7 +23686,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -25040,7 +25060,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -25068,7 +25088,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -26442,7 +26462,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -26470,7 +26490,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -27844,7 +27864,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -27872,7 +27892,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -29246,7 +29266,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -29274,7 +29294,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -30648,7 +30668,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -30676,7 +30696,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -32050,7 +32070,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -32078,7 +32098,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -33452,7 +33472,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -33480,7 +33500,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -34854,7 +34874,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -34882,7 +34902,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -36256,7 +36276,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -36284,7 +36304,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -40431,7 +40451,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -40459,7 +40479,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -41833,7 +41853,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -41861,7 +41881,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -43235,7 +43255,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -43263,7 +43283,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -44637,7 +44657,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -44665,7 +44685,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -46039,7 +46059,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -46067,7 +46087,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -47438,7 +47458,7 @@
       <c r="L4" s="384"/>
       <c r="M4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="N4" s="387"/>
       <c r="O4" s="387"/>
@@ -47466,7 +47486,7 @@
       <c r="L5" s="384"/>
       <c r="M5" s="387">
         <f ca="1">M4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="N5" s="383"/>
       <c r="O5" s="383"/>
@@ -53664,7 +53684,7 @@
       <c r="G3" s="379"/>
       <c r="H3" s="376">
         <f ca="1">+'1'!N4:N4</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="I3" s="376"/>
       <c r="J3" s="377"/>
@@ -55121,7 +55141,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -55149,7 +55169,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -56533,7 +56553,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -56561,7 +56581,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -57940,7 +57960,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -57968,7 +57988,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -59347,7 +59367,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -59375,7 +59395,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
@@ -60017,6 +60037,9 @@
       <c r="P20" s="119">
         <f t="shared" si="5"/>
         <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>6</v>
       </c>
       <c r="R20">
         <f>P20/21</f>
@@ -60752,7 +60775,7 @@
       <c r="M4" s="384"/>
       <c r="N4" s="387">
         <f ca="1">TODAY()+1</f>
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="387"/>
       <c r="P4" s="387"/>
@@ -60780,7 +60803,7 @@
       <c r="M5" s="384"/>
       <c r="N5" s="387">
         <f ca="1">N4-1</f>
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="383"/>
       <c r="P5" s="383"/>
